--- a/GameDesign/策划文档/梦境属性.xlsx
+++ b/GameDesign/策划文档/梦境属性.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitDreamJourney\GameDesign\策划文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B713D83B-886F-4562-A421-15E69B5365EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B0D215-60BC-4828-BB7E-B2A864251A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -550,7 +550,7 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
